--- a/artfynd/A 11852-2026 artfynd.xlsx
+++ b/artfynd/A 11852-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132015470</v>
       </c>
       <c r="B2" t="n">
-        <v>80239</v>
+        <v>80240</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132015490</v>
+        <v>132015453</v>
       </c>
       <c r="B3" t="n">
-        <v>80373</v>
+        <v>57907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,26 +807,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504190</v>
+        <v>504262</v>
       </c>
       <c r="R3" t="n">
-        <v>7001657</v>
+        <v>7001619</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,34 +877,38 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -917,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132015476</v>
+        <v>132015490</v>
       </c>
       <c r="B4" t="n">
-        <v>57903</v>
+        <v>80374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,50 +937,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Singån-Svartmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504218</v>
+        <v>504190</v>
       </c>
       <c r="R4" t="n">
-        <v>7001616</v>
+        <v>7001657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,6 +1008,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,9 +1017,19 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Lövrik barrblandskog med bitvis stort inslag av äldre aspar.</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1040,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132015453</v>
+        <v>132015476</v>
       </c>
       <c r="B5" t="n">
-        <v>57906</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,16 +1058,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1068,25 +1075,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Singån-Svartmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504262</v>
+        <v>504218</v>
       </c>
       <c r="R5" t="n">
-        <v>7001619</v>
+        <v>7001616</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,11 +1136,6 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1137,22 +1147,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Lövrik barrblandskog med bitvis stort inslag av äldre aspar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132015489</v>
+        <v>132015478</v>
       </c>
       <c r="B6" t="n">
-        <v>80277</v>
+        <v>80278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504246</v>
+        <v>504211</v>
       </c>
       <c r="R6" t="n">
-        <v>7001621</v>
+        <v>7001623</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
         <v>132015487</v>
       </c>
       <c r="B7" t="n">
-        <v>80277</v>
+        <v>80278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132015478</v>
+        <v>132015489</v>
       </c>
       <c r="B8" t="n">
-        <v>80277</v>
+        <v>80278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504211</v>
+        <v>504246</v>
       </c>
       <c r="R8" t="n">
-        <v>7001623</v>
+        <v>7001621</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
         <v>132015471</v>
       </c>
       <c r="B9" t="n">
-        <v>80239</v>
+        <v>80240</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>132015454</v>
       </c>
       <c r="B10" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>132015485</v>
       </c>
       <c r="B11" t="n">
-        <v>80277</v>
+        <v>80278</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>132015491</v>
       </c>
       <c r="B12" t="n">
-        <v>80373</v>
+        <v>80374</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2026,42 +2026,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132015452</v>
+        <v>132015481</v>
       </c>
       <c r="B13" t="n">
-        <v>57906</v>
+        <v>80278</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2069,10 +2064,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504192</v>
+        <v>504076</v>
       </c>
       <c r="R13" t="n">
-        <v>7001611</v>
+        <v>7001655</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,38 +2102,34 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2156,37 +2147,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132015492</v>
+        <v>132015468</v>
       </c>
       <c r="B14" t="n">
-        <v>80373</v>
+        <v>80403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2194,10 +2189,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504259</v>
+        <v>504258</v>
       </c>
       <c r="R14" t="n">
-        <v>7001667</v>
+        <v>7001671</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2244,7 +2239,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2277,41 +2272,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132015468</v>
+        <v>132015497</v>
       </c>
       <c r="B15" t="n">
-        <v>80402</v>
+        <v>80374</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2319,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504258</v>
+        <v>504190</v>
       </c>
       <c r="R15" t="n">
-        <v>7001671</v>
+        <v>7001681</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2369,22 +2360,22 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2405,7 +2396,7 @@
         <v>132015483</v>
       </c>
       <c r="B16" t="n">
-        <v>80277</v>
+        <v>80278</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2523,32 +2514,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132015481</v>
+        <v>132015492</v>
       </c>
       <c r="B17" t="n">
-        <v>80277</v>
+        <v>80374</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2561,10 +2552,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504076</v>
+        <v>504259</v>
       </c>
       <c r="R17" t="n">
-        <v>7001655</v>
+        <v>7001667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2616,17 +2607,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2644,10 +2635,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132015497</v>
+        <v>132015452</v>
       </c>
       <c r="B18" t="n">
-        <v>80373</v>
+        <v>57907</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,26 +2646,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2682,10 +2678,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504190</v>
+        <v>504192</v>
       </c>
       <c r="R18" t="n">
-        <v>7001681</v>
+        <v>7001611</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2720,34 +2716,38 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2768,7 +2768,7 @@
         <v>132015500</v>
       </c>
       <c r="B19" t="n">
-        <v>80333</v>
+        <v>80334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2886,32 +2886,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132015484</v>
+        <v>132015472</v>
       </c>
       <c r="B20" t="n">
-        <v>80277</v>
+        <v>80240</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>388</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504240</v>
+        <v>504152</v>
       </c>
       <c r="R20" t="n">
-        <v>7001684</v>
+        <v>7001666</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132015472</v>
+        <v>132015503</v>
       </c>
       <c r="B21" t="n">
-        <v>80239</v>
+        <v>79269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3018,25 +3018,33 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -3045,10 +3053,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504152</v>
+        <v>504303</v>
       </c>
       <c r="R21" t="n">
-        <v>7001666</v>
+        <v>7001661</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3083,6 +3091,11 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav här.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3095,22 +3108,22 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3128,44 +3141,36 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132015503</v>
+        <v>132015484</v>
       </c>
       <c r="B22" t="n">
-        <v>79268</v>
+        <v>80278</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3174,10 +3179,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504303</v>
+        <v>504240</v>
       </c>
       <c r="R22" t="n">
-        <v>7001661</v>
+        <v>7001684</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3212,11 +3217,6 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav här.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3229,22 +3229,22 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132015498</v>
+        <v>132015444</v>
       </c>
       <c r="B23" t="n">
-        <v>78280</v>
+        <v>83249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3273,21 +3273,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504301</v>
+        <v>504302</v>
       </c>
       <c r="R23" t="n">
-        <v>7001665</v>
+        <v>7001666</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3350,7 +3350,22 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3368,10 +3383,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132015444</v>
+        <v>132015498</v>
       </c>
       <c r="B24" t="n">
-        <v>83248</v>
+        <v>78281</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3379,21 +3394,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3406,10 +3421,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504302</v>
+        <v>504301</v>
       </c>
       <c r="R24" t="n">
-        <v>7001666</v>
+        <v>7001665</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3456,22 +3471,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3492,7 +3492,7 @@
         <v>132015480</v>
       </c>
       <c r="B25" t="n">
-        <v>80277</v>
+        <v>80278</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>132015455</v>
       </c>
       <c r="B26" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132015475</v>
+        <v>132015504</v>
       </c>
       <c r="B27" t="n">
-        <v>80239</v>
+        <v>79269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3778,10 +3778,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504196</v>
+        <v>504241</v>
       </c>
       <c r="R27" t="n">
-        <v>7001688</v>
+        <v>7001619</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3828,22 +3828,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3864,7 +3849,7 @@
         <v>132015505</v>
       </c>
       <c r="B28" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3967,10 +3952,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132015504</v>
+        <v>132015475</v>
       </c>
       <c r="B29" t="n">
-        <v>79268</v>
+        <v>80240</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3978,21 +3963,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4005,10 +3990,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504241</v>
+        <v>504196</v>
       </c>
       <c r="R29" t="n">
-        <v>7001619</v>
+        <v>7001688</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4055,7 +4040,22 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132015477</v>
+        <v>132015474</v>
       </c>
       <c r="B30" t="n">
-        <v>80374</v>
+        <v>80240</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4084,21 +4084,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>388</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504195</v>
+        <v>504179</v>
       </c>
       <c r="R30" t="n">
-        <v>7001681</v>
+        <v>7001678</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4194,10 +4194,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132015474</v>
+        <v>132015477</v>
       </c>
       <c r="B31" t="n">
-        <v>80239</v>
+        <v>80375</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,21 +4205,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>388</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504179</v>
+        <v>504195</v>
       </c>
       <c r="R31" t="n">
-        <v>7001678</v>
+        <v>7001681</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4318,7 +4318,7 @@
         <v>132015482</v>
       </c>
       <c r="B32" t="n">
-        <v>80277</v>
+        <v>80278</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>132015495</v>
       </c>
       <c r="B33" t="n">
-        <v>80373</v>
+        <v>80374</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>132015456</v>
       </c>
       <c r="B34" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>132015493</v>
       </c>
       <c r="B35" t="n">
-        <v>80373</v>
+        <v>80374</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>132015488</v>
       </c>
       <c r="B36" t="n">
-        <v>80277</v>
+        <v>80278</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>132015486</v>
       </c>
       <c r="B37" t="n">
-        <v>80277</v>
+        <v>80278</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>132015479</v>
       </c>
       <c r="B38" t="n">
-        <v>80277</v>
+        <v>80278</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>132015494</v>
       </c>
       <c r="B39" t="n">
-        <v>80373</v>
+        <v>80374</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 11852-2026 artfynd.xlsx
+++ b/artfynd/A 11852-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132015470</v>
       </c>
       <c r="B2" t="n">
-        <v>80240</v>
+        <v>80245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132015453</v>
+        <v>132015476</v>
       </c>
       <c r="B3" t="n">
-        <v>57907</v>
+        <v>57909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,25 +824,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Singån-Svartmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504262</v>
+        <v>504218</v>
       </c>
       <c r="R3" t="n">
-        <v>7001619</v>
+        <v>7001616</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,11 +885,6 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -893,22 +896,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Lövrik barrblandskog med bitvis stort inslag av äldre aspar.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -929,7 +922,7 @@
         <v>132015490</v>
       </c>
       <c r="B4" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132015476</v>
+        <v>132015453</v>
       </c>
       <c r="B5" t="n">
-        <v>57904</v>
+        <v>57912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,16 +1051,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1075,33 +1068,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Singån-Svartmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504218</v>
+        <v>504262</v>
       </c>
       <c r="R5" t="n">
-        <v>7001616</v>
+        <v>7001619</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,6 +1121,11 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1147,12 +1137,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Lövrik barrblandskog med bitvis stort inslag av äldre aspar.</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
         <v>132015478</v>
       </c>
       <c r="B6" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>132015487</v>
       </c>
       <c r="B7" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>132015489</v>
       </c>
       <c r="B8" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>132015471</v>
       </c>
       <c r="B9" t="n">
-        <v>80240</v>
+        <v>80245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,42 +1654,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132015454</v>
+        <v>132015485</v>
       </c>
       <c r="B10" t="n">
-        <v>57907</v>
+        <v>80283</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1697,10 +1692,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504284</v>
+        <v>504254</v>
       </c>
       <c r="R10" t="n">
-        <v>7001590</v>
+        <v>7001622</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1735,38 +1730,34 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1784,32 +1775,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132015485</v>
+        <v>132015491</v>
       </c>
       <c r="B11" t="n">
-        <v>80278</v>
+        <v>80379</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1822,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504254</v>
+        <v>504239</v>
       </c>
       <c r="R11" t="n">
-        <v>7001622</v>
+        <v>7001691</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1905,10 +1896,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132015491</v>
+        <v>132015454</v>
       </c>
       <c r="B12" t="n">
-        <v>80374</v>
+        <v>57912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,26 +1907,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1943,10 +1939,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504239</v>
+        <v>504284</v>
       </c>
       <c r="R12" t="n">
-        <v>7001691</v>
+        <v>7001590</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1981,34 +1977,38 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2029,7 +2029,7 @@
         <v>132015481</v>
       </c>
       <c r="B13" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>132015468</v>
       </c>
       <c r="B14" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>132015497</v>
       </c>
       <c r="B15" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>132015483</v>
       </c>
       <c r="B16" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>132015492</v>
       </c>
       <c r="B17" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>132015452</v>
       </c>
       <c r="B18" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>132015500</v>
       </c>
       <c r="B19" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>132015472</v>
       </c>
       <c r="B20" t="n">
-        <v>80240</v>
+        <v>80245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>132015503</v>
       </c>
       <c r="B21" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>132015484</v>
       </c>
       <c r="B22" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132015444</v>
+        <v>132015498</v>
       </c>
       <c r="B23" t="n">
-        <v>83249</v>
+        <v>78286</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3273,21 +3273,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504302</v>
+        <v>504301</v>
       </c>
       <c r="R23" t="n">
-        <v>7001666</v>
+        <v>7001665</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3350,22 +3350,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3383,10 +3368,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132015498</v>
+        <v>132015444</v>
       </c>
       <c r="B24" t="n">
-        <v>78281</v>
+        <v>83254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3394,21 +3379,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3421,10 +3406,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504301</v>
+        <v>504302</v>
       </c>
       <c r="R24" t="n">
-        <v>7001665</v>
+        <v>7001666</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3471,7 +3456,22 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3492,7 +3492,7 @@
         <v>132015480</v>
       </c>
       <c r="B25" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>132015455</v>
       </c>
       <c r="B26" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132015504</v>
+        <v>132015505</v>
       </c>
       <c r="B27" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3778,10 +3778,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504241</v>
+        <v>504265</v>
       </c>
       <c r="R27" t="n">
-        <v>7001619</v>
+        <v>7001606</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132015505</v>
+        <v>132015504</v>
       </c>
       <c r="B28" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504265</v>
+        <v>504241</v>
       </c>
       <c r="R28" t="n">
-        <v>7001606</v>
+        <v>7001619</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
         <v>132015475</v>
       </c>
       <c r="B29" t="n">
-        <v>80240</v>
+        <v>80245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>132015474</v>
       </c>
       <c r="B30" t="n">
-        <v>80240</v>
+        <v>80245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>132015477</v>
       </c>
       <c r="B31" t="n">
-        <v>80375</v>
+        <v>80380</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>132015482</v>
       </c>
       <c r="B32" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>132015495</v>
       </c>
       <c r="B33" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>132015456</v>
       </c>
       <c r="B34" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>132015493</v>
       </c>
       <c r="B35" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>132015488</v>
       </c>
       <c r="B36" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>132015486</v>
       </c>
       <c r="B37" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>132015479</v>
       </c>
       <c r="B38" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>132015494</v>
       </c>
       <c r="B39" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 11852-2026 artfynd.xlsx
+++ b/artfynd/A 11852-2026 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132015476</v>
+        <v>132015490</v>
       </c>
       <c r="B3" t="n">
-        <v>57909</v>
+        <v>80379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,50 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Singån-Svartmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504218</v>
+        <v>504190</v>
       </c>
       <c r="R3" t="n">
-        <v>7001616</v>
+        <v>7001657</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,9 +887,19 @@
           <t>Barr-/lövbland</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Lövrik barrblandskog med bitvis stort inslag av äldre aspar.</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132015490</v>
+        <v>132015453</v>
       </c>
       <c r="B4" t="n">
-        <v>80379</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,26 +928,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504190</v>
+        <v>504262</v>
       </c>
       <c r="R4" t="n">
-        <v>7001657</v>
+        <v>7001619</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,34 +998,38 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1040,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132015453</v>
+        <v>132015476</v>
       </c>
       <c r="B5" t="n">
-        <v>57912</v>
+        <v>57909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,16 +1058,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1068,25 +1075,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Singån-Svartmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504262</v>
+        <v>504218</v>
       </c>
       <c r="R5" t="n">
-        <v>7001619</v>
+        <v>7001616</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,11 +1136,6 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1137,22 +1147,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Lövrik barrblandskog med bitvis stort inslag av äldre aspar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 11852-2026 artfynd.xlsx
+++ b/artfynd/A 11852-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132015470</v>
       </c>
       <c r="B2" t="n">
-        <v>80245</v>
+        <v>80247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>132015490</v>
       </c>
       <c r="B3" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>132015453</v>
       </c>
       <c r="B4" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>132015476</v>
       </c>
       <c r="B5" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>132015478</v>
       </c>
       <c r="B6" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>132015487</v>
       </c>
       <c r="B7" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>132015489</v>
       </c>
       <c r="B8" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>132015471</v>
       </c>
       <c r="B9" t="n">
-        <v>80245</v>
+        <v>80247</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>132015485</v>
       </c>
       <c r="B10" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>132015491</v>
       </c>
       <c r="B11" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>132015454</v>
       </c>
       <c r="B12" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>132015481</v>
       </c>
       <c r="B13" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>132015468</v>
       </c>
       <c r="B14" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>132015497</v>
       </c>
       <c r="B15" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>132015483</v>
       </c>
       <c r="B16" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>132015492</v>
       </c>
       <c r="B17" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>132015452</v>
       </c>
       <c r="B18" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>132015500</v>
       </c>
       <c r="B19" t="n">
-        <v>80339</v>
+        <v>80341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>132015472</v>
       </c>
       <c r="B20" t="n">
-        <v>80245</v>
+        <v>80247</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>132015503</v>
       </c>
       <c r="B21" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>132015484</v>
       </c>
       <c r="B22" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>132015498</v>
       </c>
       <c r="B23" t="n">
-        <v>78286</v>
+        <v>78288</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>132015444</v>
       </c>
       <c r="B24" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>132015480</v>
       </c>
       <c r="B25" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>132015455</v>
       </c>
       <c r="B26" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132015505</v>
+        <v>132015504</v>
       </c>
       <c r="B27" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3778,10 +3778,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504265</v>
+        <v>504241</v>
       </c>
       <c r="R27" t="n">
-        <v>7001606</v>
+        <v>7001619</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132015504</v>
+        <v>132015505</v>
       </c>
       <c r="B28" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504241</v>
+        <v>504265</v>
       </c>
       <c r="R28" t="n">
-        <v>7001619</v>
+        <v>7001606</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
         <v>132015475</v>
       </c>
       <c r="B29" t="n">
-        <v>80245</v>
+        <v>80247</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>132015474</v>
       </c>
       <c r="B30" t="n">
-        <v>80245</v>
+        <v>80247</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>132015477</v>
       </c>
       <c r="B31" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>132015482</v>
       </c>
       <c r="B32" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>132015495</v>
       </c>
       <c r="B33" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>132015456</v>
       </c>
       <c r="B34" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>132015493</v>
       </c>
       <c r="B35" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>132015488</v>
       </c>
       <c r="B36" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>132015486</v>
       </c>
       <c r="B37" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>132015479</v>
       </c>
       <c r="B38" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>132015494</v>
       </c>
       <c r="B39" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
